--- a/tests/fixtures/controls/C10075/package/emr_workbook_Q2_2026.xlsx
+++ b/tests/fixtures/controls/C10075/package/emr_workbook_Q2_2026.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dana.wu@hp.com</t>
+          <t>dana.wu@example.com</t>
         </is>
       </c>
     </row>
